--- a/Data/FIA/c_selected_FIA.xlsx
+++ b/Data/FIA/c_selected_FIA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mai00099/maia1/260807_FIA_exploration/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maimac/maia1/Data/FIA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{611C0C1C-A6D8-074D-997E-229E10E4AAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B09DA0E-D78D-244A-9563-039E79C3FBD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17740" yWindow="600" windowWidth="20660" windowHeight="19720" xr2:uid="{908D2EE9-B1A3-AC43-8CAD-20CBBF233E88}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="15740" xr2:uid="{908D2EE9-B1A3-AC43-8CAD-20CBBF233E88}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -998,7 +998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="136" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="151" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>33</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="145" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="157" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
         <v>79</v>
       </c>
